--- a/outputs/milk/novus/primary_chain_output.xlsx
+++ b/outputs/milk/novus/primary_chain_output.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PreTests" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ModelCoefficients" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ResidualDiagnostics" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SeriesUsed" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LagProfile" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ModelEligibility" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NARDL_Multipliers" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VECM_IRF" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="PreTests" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ModelCoefficients" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ResidualDiagnostics" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="SeriesUsed" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="LagProfile" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="ModelEligibility" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="NARDL_Multipliers" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="VECM_IRF" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -518,19 +518,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01248306245783195</v>
+        <v>0.01248306245784421</v>
       </c>
       <c r="C2" t="n">
         <v>0.01</v>
       </c>
       <c r="D2" t="n">
-        <v>4.729732285866721e-13</v>
+        <v>4.729732285868142e-13</v>
       </c>
       <c r="E2" t="n">
         <v>0.1</v>
       </c>
       <c r="F2" t="n">
-        <v>1.068911264269411e-21</v>
+        <v>1.068911264269473e-21</v>
       </c>
       <c r="G2" t="n">
         <v>0.1</v>
@@ -574,13 +574,13 @@
         <v>0.01</v>
       </c>
       <c r="D3" t="n">
-        <v>3.818978011570181e-13</v>
+        <v>3.818978011570844e-13</v>
       </c>
       <c r="E3" t="n">
         <v>0.1</v>
       </c>
       <c r="F3" t="n">
-        <v>4.4125656034645e-11</v>
+        <v>4.41256560346402e-11</v>
       </c>
       <c r="G3" t="n">
         <v>0.1</v>
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.0747088730315122</v>
+        <v>0.07470887303151186</v>
       </c>
       <c r="N5" t="n">
         <v>201</v>
@@ -926,10 +926,10 @@
         <v>201</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6442401315402562</v>
+        <v>0.6442401315402435</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.2843166259159834</v>
+        <v>-0.2843166259159418</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
@@ -1000,16 +1000,16 @@
         <v>197</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.002155003969288638</v>
+        <v>-0.002155003969288249</v>
       </c>
       <c r="K3" t="n">
         <v>-0.3006834081052232</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.9538372381620318</v>
+        <v>-0.9538372381620321</v>
       </c>
       <c r="M3" t="n">
-        <v>3.295228800215539e-21</v>
+        <v>3.295228800215894e-21</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -1078,22 +1078,22 @@
         <v>199</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0146434053790121</v>
+        <v>0.01464340537901077</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.7451033547254826</v>
+        <v>-0.7451033547254802</v>
       </c>
       <c r="L4" t="n">
         <v>-1.091145579024727</v>
       </c>
       <c r="M4" t="n">
-        <v>2.210764505250913e-26</v>
+        <v>2.210764505227035e-26</v>
       </c>
       <c r="N4" t="n">
-        <v>0.9865928543793412</v>
+        <v>0.9865928543792826</v>
       </c>
       <c r="O4" t="n">
-        <v>0.01665697627998265</v>
+        <v>0.016656976279983</v>
       </c>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr">
@@ -1193,13 +1193,13 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.9979470328795065</v>
+        <v>0.997947032879507</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2079845355603383</v>
+        <v>0.2079845355601896</v>
       </c>
       <c r="G2" t="n">
-        <v>2.474090685541242e-48</v>
+        <v>2.474090685540177e-48</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -1227,13 +1227,13 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.153692432382161</v>
+        <v>0.1536924323821612</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00213984567239458</v>
+        <v>0.002139845672394596</v>
       </c>
       <c r="G3" t="n">
-        <v>4.744864281636172e-221</v>
+        <v>4.744864281639144e-221</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
@@ -1261,13 +1261,13 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.1477169652972014</v>
+        <v>0.1477169652972021</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0004696321631414695</v>
+        <v>0.0004696321631414275</v>
       </c>
       <c r="G4" t="n">
-        <v>8.675957601558099e-203</v>
+        <v>8.675957601562549e-203</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
@@ -57253,7 +57253,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>-1.774293874103992</v>
+        <v>-1.774293874103995</v>
       </c>
       <c r="C2" t="n">
         <v>-1.788937279483005</v>
@@ -57269,10 +57269,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>-1.896552577620362</v>
+        <v>-1.896552577620365</v>
       </c>
       <c r="C3" t="n">
-        <v>-1.912204994969054</v>
+        <v>-1.912204994969057</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -57285,10 +57285,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>-1.904976881397576</v>
+        <v>-1.90497688139758</v>
       </c>
       <c r="C4" t="n">
-        <v>-1.920698825275694</v>
+        <v>-1.920698825275696</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -57301,10 +57301,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>-1.905557362721929</v>
+        <v>-1.905557362721933</v>
       </c>
       <c r="C5" t="n">
-        <v>-1.92128409736412</v>
+        <v>-1.921284097364122</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -57317,10 +57317,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>-1.90559736110955</v>
+        <v>-1.905597361109554</v>
       </c>
       <c r="C6" t="n">
-        <v>-1.921324425861997</v>
+        <v>-1.921324425861999</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -57333,10 +57333,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>-1.905600117220635</v>
+        <v>-1.905600117220639</v>
       </c>
       <c r="C7" t="n">
-        <v>-1.921327204719512</v>
+        <v>-1.921327204719514</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -57349,10 +57349,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>-1.905600307131998</v>
+        <v>-1.905600307132002</v>
       </c>
       <c r="C8" t="n">
-        <v>-1.92132739619823</v>
+        <v>-1.921327396198232</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -57365,10 +57365,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>-1.905600320217945</v>
+        <v>-1.905600320217949</v>
       </c>
       <c r="C9" t="n">
-        <v>-1.921327409392177</v>
+        <v>-1.92132740939218</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -57381,10 +57381,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>-1.90560032111964</v>
+        <v>-1.905600321119644</v>
       </c>
       <c r="C10" t="n">
-        <v>-1.921327410301313</v>
+        <v>-1.921327410301316</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -57397,10 +57397,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>-1.905600321181772</v>
+        <v>-1.905600321181776</v>
       </c>
       <c r="C11" t="n">
-        <v>-1.921327410363958</v>
+        <v>-1.921327410363961</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -57413,10 +57413,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>-1.905600321186053</v>
+        <v>-1.905600321186057</v>
       </c>
       <c r="C12" t="n">
-        <v>-1.921327410368274</v>
+        <v>-1.921327410368277</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -57429,10 +57429,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>-1.905600321186348</v>
+        <v>-1.905600321186352</v>
       </c>
       <c r="C13" t="n">
-        <v>-1.921327410368572</v>
+        <v>-1.921327410368574</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -57445,10 +57445,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>-1.905600321186368</v>
+        <v>-1.905600321186372</v>
       </c>
       <c r="C14" t="n">
-        <v>-1.921327410368592</v>
+        <v>-1.921327410368595</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -57461,10 +57461,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>-1.90560032118637</v>
+        <v>-1.905600321186374</v>
       </c>
       <c r="C15" t="n">
-        <v>-1.921327410368594</v>
+        <v>-1.921327410368596</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -57477,10 +57477,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>-1.90560032118637</v>
+        <v>-1.905600321186374</v>
       </c>
       <c r="C16" t="n">
-        <v>-1.921327410368594</v>
+        <v>-1.921327410368596</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -57493,10 +57493,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>-1.90560032118637</v>
+        <v>-1.905600321186374</v>
       </c>
       <c r="C17" t="n">
-        <v>-1.921327410368594</v>
+        <v>-1.921327410368596</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -57509,10 +57509,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>-1.90560032118637</v>
+        <v>-1.905600321186374</v>
       </c>
       <c r="C18" t="n">
-        <v>-1.921327410368594</v>
+        <v>-1.921327410368596</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -57525,10 +57525,10 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>-1.90560032118637</v>
+        <v>-1.905600321186374</v>
       </c>
       <c r="C19" t="n">
-        <v>-1.921327410368594</v>
+        <v>-1.921327410368596</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -57541,10 +57541,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>-1.90560032118637</v>
+        <v>-1.905600321186374</v>
       </c>
       <c r="C20" t="n">
-        <v>-1.921327410368594</v>
+        <v>-1.921327410368596</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -57557,10 +57557,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>-1.90560032118637</v>
+        <v>-1.905600321186374</v>
       </c>
       <c r="C21" t="n">
-        <v>-1.921327410368594</v>
+        <v>-1.921327410368596</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -57573,10 +57573,10 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>-1.90560032118637</v>
+        <v>-1.905600321186374</v>
       </c>
       <c r="C22" t="n">
-        <v>-1.921327410368594</v>
+        <v>-1.921327410368596</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
